--- a/tame_output/ON/bt/strategyON_20240509.xlsx
+++ b/tame_output/ON/bt/strategyON_20240509.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.0%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.0%</t>
+          <t>441.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.5%</t>
+          <t>-612.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-147.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.9%</t>
+          <t>-287.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.2%</t>
+          <t>-155.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270.8%</t>
+          <t>-254.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-205.2%</t>
+          <t>-195.2%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.752374257840131</v>
+        <v>-9.87369490617689</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.753083333555959</v>
+        <v>-0.8016115928906626</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.712189959473941</v>
+        <v>-9.8335106078107</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7366659903216415</v>
+        <v>-0.7851942496563451</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.632120163936136</v>
+        <v>-9.753440812272895</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7052712508857626</v>
+        <v>-0.7537995102204662</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.398638941706537</v>
+        <v>-9.519959590043296</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6039543331560706</v>
+        <v>-0.6524825924907742</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.218930411562663</v>
+        <v>-9.340251059899423</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5349631314114802</v>
+        <v>-0.5834913907461838</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.086654937931776</v>
+        <v>-9.207975586268535</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4866854552120983</v>
+        <v>-0.5352137145468019</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.896055263258623</v>
+        <v>-9.017375911595382</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4076305246552003</v>
+        <v>-0.4561587839899039</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.647055464575041</v>
+        <v>-8.768376112911801</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2951242639581091</v>
+        <v>-0.3436525232928127</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.752645454348146</v>
+        <v>-8.873966102684905</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4653361894665693</v>
+        <v>-0.5138644488012734</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.771380356466743</v>
+        <v>-8.892701004803502</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4242858084369221</v>
+        <v>-0.4728140677716257</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.623440315059144</v>
+        <v>-8.744760963395903</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4849887145620499</v>
+        <v>-0.5335169738967536</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.599211678670171</v>
+        <v>-8.72053232700693</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4840112462599389</v>
+        <v>-0.5325395055946425</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.55566327189948</v>
+        <v>-8.676983920236239</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4735524956467554</v>
+        <v>-0.5220807549814594</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.313514878445622</v>
+        <v>-8.434835526782381</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.362230783884069</v>
+        <v>-0.4107590432187731</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.250285506677274</v>
+        <v>-8.371606155014033</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.342406914717535</v>
+        <v>-0.3909351740522391</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.126994371860144</v>
+        <v>-8.248315020196904</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2955923667801064</v>
+        <v>-0.34412062611481</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.105845172956702</v>
+        <v>-8.227165821293461</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.279431708981404</v>
+        <v>-0.3279599683161081</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.862079730973258</v>
+        <v>-7.983400379310017</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.186144823840976</v>
+        <v>-0.2346730831756796</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.598051663779998</v>
+        <v>-7.719372312116757</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.0784092830436558</v>
+        <v>-0.1269375423783599</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.348201269830923</v>
+        <v>-7.469521918167683</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01427294951967584</v>
+        <v>-0.03425530981502778</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.172309177363491</v>
+        <v>-7.293629825700251</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08822891002729749</v>
+        <v>0.03970065069259388</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.000862714341028</v>
+        <v>-7.122183362677787</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1701350012908365</v>
+        <v>0.1216067419561329</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.775829714672205</v>
+        <v>-6.897150363008964</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.259168678774663</v>
+        <v>0.2106404194399589</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.561195337035798</v>
+        <v>-6.682515985372557</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.349717230883543</v>
+        <v>0.3011889715488389</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.4681952958299</v>
+        <v>-6.589515944166659</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3681115061496976</v>
+        <v>0.3195832468149939</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.22776479902504</v>
+        <v>-6.349085447361799</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4660267814965193</v>
+        <v>0.4174985221618157</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.155522230853845</v>
+        <v>-6.276842879190604</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.4988531225998174</v>
+        <v>0.4503248632651138</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.03958238122866</v>
+        <v>-6.160903029565419</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5459076463672314</v>
+        <v>0.4973793870325278</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7928545650463659</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972339</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.796926792805497</v>
+        <v>-5.918247441142256</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6399679529564901</v>
+        <v>0.5914396936217865</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7928545650463659</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.576905994768486</v>
+        <v>-5.698226643105246</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7295553091819085</v>
+        <v>0.6810270498472049</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6516347199783856</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.377657364863677</v>
+        <v>-5.498978013200436</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8251489439456554</v>
+        <v>0.7766206846109518</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6516347199783856</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.218142261344307</v>
+        <v>-5.339462909681067</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8901008297937052</v>
+        <v>0.8415725704590016</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4921196164590157</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.07347011624457</v>
+        <v>-5.194790764581329</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9580577903950402</v>
+        <v>0.9095295310603362</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3474474713592783</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.133344943602262</v>
+        <v>-5.254665591939021</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9201453508533888</v>
+        <v>0.8716170915186852</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4073222987169704</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.046545445823254</v>
+        <v>-5.167866094160013</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9772656432875584</v>
+        <v>0.9287373839528548</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4073222987169704</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.04901515228506</v>
+        <v>-5.170335800621819</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.976350162076248</v>
+        <v>0.9278219027415444</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4097920051787766</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.11738533860907</v>
+        <v>-5.238705986945829</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9600090100213459</v>
+        <v>0.9114807506866422</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4005163061425616</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.995968908982594</v>
+        <v>-5.117289557319353</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9990122905038279</v>
+        <v>0.9504840311691241</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4005163061425616</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.026962068311299</v>
+        <v>-5.148282716648058</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8113245918127325</v>
+        <v>0.7627963324780289</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4005163061425616</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.851487808518829</v>
+        <v>-4.972808456855589</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8860815277215082</v>
+        <v>0.8375532683868046</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.817507553149952</v>
+        <v>-5.083744709496838</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8754156586302664</v>
+        <v>0.7689207960915119</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.020534130693185</v>
+        <v>-5.286771287040071</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7973364128328786</v>
+        <v>0.6908415502941243</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.862608531757892</v>
+        <v>-5.128845688104778</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8706790388391283</v>
+        <v>0.7641841763003741</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.01092978556902</v>
+        <v>-5.277166941915906</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8062968078885371</v>
+        <v>0.6998019453497828</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.012112870220081</v>
+        <v>-5.278350026566967</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7975993494726383</v>
+        <v>0.691104486933884</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.888985163225998</v>
+        <v>-5.155222319572884</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8474023053033732</v>
+        <v>0.7409074427646187</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.796174681775138</v>
+        <v>-5.062411838122024</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8137991897750827</v>
+        <v>0.7073043272363284</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.747611629554108</v>
+        <v>-5.013848785900994</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8350978865880956</v>
+        <v>0.7286030240493413</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.634940411317858</v>
+        <v>-4.901177567664744</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8752420823943186</v>
+        <v>0.7687472198555643</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.522563410135185</v>
+        <v>-4.788800566482071</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.925684178698055</v>
+        <v>0.8191893161593007</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.720797979021916</v>
+        <v>-4.987035135368802</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8578875529119017</v>
+        <v>0.7513926903731474</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.803799260047195</v>
+        <v>-5.070036416394081</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6630427605024434</v>
+        <v>0.5565478979636889</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.644604987990618</v>
+        <v>-4.910842144337504</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8468701300442798</v>
+        <v>0.7403752675055253</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.731203570971721</v>
+        <v>-4.997440727318607</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8267437229541614</v>
+        <v>0.7202488604154071</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.69281990841357</v>
+        <v>-4.959057064760456</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8395166293197907</v>
+        <v>0.7330217667810364</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.515703578378404</v>
+        <v>-4.78194073472529</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9070921901791591</v>
+        <v>0.8005973276404046</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.486001454402111</v>
+        <v>-4.752238610748996</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9196564315315896</v>
+        <v>0.8131615689928351</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.75072580148124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.306626033163343</v>
+        <v>-4.572863189510229</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.985193575333511</v>
+        <v>0.8786987127947565</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3812563381445147</v>
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.830963123247486</v>
+        <v>3.489090507066867</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.489753020932412</v>
+        <v>-4.512125274417783</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8927502355574732</v>
+        <v>0.8838013341633246</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4681071894770567</v>
+        <v>-0.3009926357637203</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.408143554557951</v>
+        <v>2.508412286785953</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240509.xlsx
+++ b/tame_output/ON/bt/strategyON_20240509.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>134.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.1%</t>
+          <t>444.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-612.8%</t>
+          <t>-595.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-44.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-147.0%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.8%</t>
+          <t>-280.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-254.1%</t>
+          <t>-257.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-195.2%</t>
+          <t>-197.4%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.805145726365682</v>
+        <v>-8.646473517011048</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.405252560037427</v>
+        <v>-0.3417836762955733</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.73618879205209</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031190560923552</v>
+        <v>2.07544887959134</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.238494834475917</v>
+        <v>-9.079822625121283</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5826185078159245</v>
+        <v>-0.5191496240740707</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.73618879205209</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027164256389149</v>
+        <v>2.071422575056936</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.621496223218548</v>
+        <v>-9.462824013863914</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7359211646345609</v>
+        <v>-0.6724522808927071</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.73618879205209</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027062155067564</v>
+        <v>2.071320473735352</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.778895103431669</v>
+        <v>-9.620222894077035</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7963092007483792</v>
+        <v>-0.7328403170065254</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.893587672265211</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>1.97945266157891</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13842542593567</v>
+        <v>-9.979753216581036</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9347710264519291</v>
+        <v>-0.8713021427100758</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.893587672265211</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>1.98480296487696</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46482545460068</v>
+        <v>-10.30615324524605</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.057415017960758</v>
+        <v>-0.9939461342189033</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.219987700930224</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.79687896763513</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68397442267488</v>
+        <v>-10.52530221332025</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.142032854568667</v>
+        <v>-1.078563970826814</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.439136669004421</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.66843133741238</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.68028349771847</v>
+        <v>-10.52161128836384</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.140556484586103</v>
+        <v>-1.077087600844249</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.439136669004421</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.66843133741238</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88454167304833</v>
+        <v>-10.7258694636937</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.216746557599406</v>
+        <v>-1.153277673857552</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.56677561361841</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.597361167762629</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10257944467951</v>
+        <v>-10.94390723532488</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.299479111767441</v>
+        <v>-1.236010228025588</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.741546381714309</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.496981261389526</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02910961301206</v>
+        <v>-10.87043740365743</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254719477607041</v>
+        <v>-1.191250593865187</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.668076550046861</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.556434861883416</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20423403039861</v>
+        <v>-11.04556182104397</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.310214023814141</v>
+        <v>-1.246745140072287</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.843200967433404</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.465915432199006</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4386861244131</v>
+        <v>-11.28001391505846</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.411214026321533</v>
+        <v>-1.347745142579679</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.843200967433404</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.45869626729741</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72648996895033</v>
+        <v>-11.5678177595957</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.533007754910404</v>
+        <v>-1.469538871168551</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.131004811970643</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.279341769801091</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95631441611416</v>
+        <v>-11.79764220675952</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623821743937378</v>
+        <v>-1.560352860195525</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.293652349040803</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.182869037397551</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18834333585042</v>
+        <v>-12.02967112649579</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713939583202768</v>
+        <v>-1.650470699460915</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.355665046229226</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.148355147713612</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13632782188161</v>
+        <v>-11.97765561252697</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.689143041928842</v>
+        <v>-1.625674158186988</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.355665046229226</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.152345483400013</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27799966360573</v>
+        <v>-12.11932745425109</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.747287005517232</v>
+        <v>-1.683818121775379</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.355665046229226</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.150870256501271</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.22840881918089</v>
+        <v>-12.06973660982626</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.712397257582426</v>
+        <v>-1.648928373840572</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.306074201804392</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.195678173321044</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.02925671194379</v>
+        <v>-11.87058450258916</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645787548334269</v>
+        <v>-1.582318664592415</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.140751675854579</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.281820555244249</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80341155922438</v>
+        <v>-11.64473934986975</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.545870414210296</v>
+        <v>-1.482401530468442</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.098825000267416</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.316555633632756</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.67883290288679</v>
+        <v>-11.52016069353216</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494899807119201</v>
+        <v>-1.431430923377346</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.098825000267416</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.317694778188815</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73172819093108</v>
+        <v>-11.57305598157644</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.513424148174807</v>
+        <v>-1.449955264432954</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.093869654178969</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.32330176000399</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44781946000233</v>
+        <v>-11.28914725064769</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.394126951564671</v>
+        <v>-1.330658067822817</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.093869654178969</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.329035464242626</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37645306739268</v>
+        <v>-11.21778085803805</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.375317656914677</v>
+        <v>-1.311848773172824</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.022503261569322</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.317859718746762</v>
+        <v>1.36211803741455</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11261620018861</v>
+        <v>-10.95394399083398</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279666391345957</v>
+        <v>-1.216197507604103</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.022503261569322</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.307976237433855</v>
+        <v>1.352234556101642</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84537439932021</v>
+        <v>-10.68670218996558</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174604231497972</v>
+        <v>-1.111135347756118</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.022503261569322</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.306141676934481</v>
+        <v>1.350399995602269</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74746736064372</v>
+        <v>-10.58879515128909</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.135741731000837</v>
+        <v>-1.072272847258982</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.028281376155078</v>
+        <v>-2.954517511708765</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.346632811877354</v>
+        <v>1.390891130545141</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.72351381966777</v>
+        <v>-10.56484161031313</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.12549180846496</v>
+        <v>-1.062022924723105</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.00432783517912</v>
+        <v>-2.930563970732808</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.361673442608422</v>
+        <v>1.40593176127621</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.45945388134497</v>
+        <v>-10.30078167199033</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.033128149297593</v>
+        <v>-0.9696592655557392</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.740267896856324</v>
+        <v>-2.666504032410012</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.506849089440348</v>
+        <v>1.551107408108135</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.87369490617689</v>
+        <v>-9.593702048485497</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8016115928906626</v>
+        <v>-0.6896144498141052</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.740267896856324</v>
+        <v>-2.666504032410012</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.504062055780047</v>
+        <v>1.548320374447834</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.8335106078107</v>
+        <v>-9.553517750119306</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7851942496563451</v>
+        <v>-0.6731971065797877</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.700083598490133</v>
+        <v>-2.626319734043821</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.528516258687603</v>
+        <v>1.57277457735539</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.753440812272895</v>
+        <v>-9.473447954581502</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7537995102204662</v>
+        <v>-0.6418023671439088</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.620013802952329</v>
+        <v>-2.546249938506017</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.575924957231042</v>
+        <v>1.620183275898829</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.519959590043296</v>
+        <v>-9.239966732351903</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6524825924907742</v>
+        <v>-0.5404854494142168</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.386532580722731</v>
+        <v>-2.312768716276418</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.723938119406654</v>
+        <v>1.768196438074441</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.340251059899423</v>
+        <v>-9.060258202208029</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5834913907461838</v>
+        <v>-0.4714942476696264</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.329361076560035</v>
+        <v>-2.255597212113722</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.755348811591312</v>
+        <v>1.799607130259099</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.207975586268535</v>
+        <v>-8.927982728577142</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5352137145468019</v>
+        <v>-0.4232165714702445</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.197085602929148</v>
+        <v>-2.123321738482836</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.830081582516871</v>
+        <v>1.874339901184658</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.017375911595382</v>
+        <v>-8.737383053903988</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4561587839899039</v>
+        <v>-0.3441616409133466</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.932722063809683</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.947256448008399</v>
+        <v>1.991514766676187</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.768376112911801</v>
+        <v>-8.488383255220407</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3436525232928127</v>
+        <v>-0.2316553802162553</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.932722063809683</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.960162789232058</v>
+        <v>2.004421107899845</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.873966102684905</v>
+        <v>-8.593973244993512</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5138644488012734</v>
+        <v>-0.401867305724716</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.1120759180291</v>
+        <v>-2.038312053582787</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.768832865768977</v>
+        <v>1.813091184436764</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.892701004803502</v>
+        <v>-8.612708147112109</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4728140677716257</v>
+        <v>-0.3608169246950683</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.1120759180291</v>
+        <v>-2.038312053582787</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.817377207646063</v>
+        <v>1.86163552631385</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.744760963395903</v>
+        <v>-8.464768105704509</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5335169738967536</v>
+        <v>-0.4215198308201962</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.091755002120542</v>
+        <v>-2.01799113767423</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70969083450303</v>
+        <v>1.753949153170817</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.72053232700693</v>
+        <v>-8.440539469315537</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5325395055946425</v>
+        <v>-0.4205423625180851</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.993762501285258</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.715514030082935</v>
+        <v>1.759772348750722</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.676983920236239</v>
+        <v>-8.396991062544846</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5220807549814594</v>
+        <v>-0.4100836119049021</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.993762501285258</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.708553417987842</v>
+        <v>1.752811736655629</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.434835526782381</v>
+        <v>-8.154842669090987</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4107590432187731</v>
+        <v>-0.2987619001422157</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.993762501285258</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.723015772368985</v>
+        <v>1.767274091036772</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.371606155014033</v>
+        <v>-8.09161329732264</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3909351740522391</v>
+        <v>-0.2789380309756817</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.993762501285258</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.71754789282818</v>
+        <v>1.761806211495967</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.248315020196904</v>
+        <v>-7.968322162505509</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.34412062611481</v>
+        <v>-0.2321234830382521</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.94423523091444</v>
+        <v>-1.870471366468128</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.789020667729035</v>
+        <v>1.833278986396822</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.227165821293461</v>
+        <v>-7.947172963602066</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3279599683161081</v>
+        <v>-0.2159628252395498</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.849322167564684</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.809411165308426</v>
+        <v>1.853669483976214</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.983400379310017</v>
+        <v>-7.703407521618622</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2346730831756796</v>
+        <v>-0.1226759400991213</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.849322167564684</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.805191873655477</v>
+        <v>1.849450192323264</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.719372312116757</v>
+        <v>-7.439379454425362</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1269375423783599</v>
+        <v>-0.01494039930180158</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.647456768748731</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.928435426865065</v>
+        <v>1.972693745532852</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.469521918167683</v>
+        <v>-7.189529060476287</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.03425530981502778</v>
+        <v>0.0777418332615305</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.647456768748731</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.921177501848767</v>
+        <v>1.965435820516555</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.293629825700251</v>
+        <v>-7.013636968008855</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.03970065069259388</v>
+        <v>0.1516977937691522</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.647456768748731</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.924776625369416</v>
+        <v>1.969034944037203</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.122183362677787</v>
+        <v>-6.842190504986392</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1216067419561329</v>
+        <v>0.2336038850326911</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.54977417017258</v>
+        <v>-1.476010305726267</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.040972009237448</v>
+        <v>2.085230327905235</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.897150363008964</v>
+        <v>-6.617157505317569</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2106404194399589</v>
+        <v>0.3226375625165172</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.324741170503757</v>
+        <v>-1.250977306057445</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.175012286655038</v>
+        <v>2.219270605322825</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.682515985372557</v>
+        <v>-6.402523127681162</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3011889715488389</v>
+        <v>0.4131861146253972</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.11010679286735</v>
+        <v>-1.036342928421038</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3084877142912</v>
+        <v>2.352746032958987</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.589515944166659</v>
+        <v>-6.309523086475264</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3195832468149939</v>
+        <v>0.4315803898915522</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.11010679286735</v>
+        <v>-1.036342928421038</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.289681973074996</v>
+        <v>2.333940291742783</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.349085447361799</v>
+        <v>-6.069092589670404</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4174985221618157</v>
+        <v>0.5294956652383735</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.7959124316161774</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.435683347782789</v>
+        <v>2.479941666450576</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.276842879190604</v>
+        <v>-5.996850021499209</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.4503248632651138</v>
+        <v>0.5623220063416716</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.7959124316161774</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.439612661617609</v>
+        <v>2.483870980285396</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.160903029565419</v>
+        <v>-5.880910171874024</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.4973793870325278</v>
+        <v>0.6093765301090861</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.7190907006000535</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.486384284144624</v>
+        <v>2.530642602812411</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.918247441142256</v>
+        <v>-5.638254583450861</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.5914396936217865</v>
+        <v>0.7034368366983443</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.7190907006000535</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.483382355364617</v>
+        <v>2.527640674032404</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.698226643105246</v>
+        <v>-5.41823378541385</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.6810270498472049</v>
+        <v>0.7930241929237627</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.5778708555320733</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.569693299416019</v>
+        <v>2.613951618083806</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.498978013200436</v>
+        <v>-5.218985155509041</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.7766206846109518</v>
+        <v>0.8886178276875096</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.5778708555320733</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.585587482217842</v>
+        <v>2.62984580088563</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.339462909681067</v>
+        <v>-5.059470051989671</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8415725704590016</v>
+        <v>0.9535697135355594</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4921196164590157</v>
+        <v>-0.4183557520127034</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.682442388769766</v>
+        <v>2.726700707437554</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.194790764581329</v>
+        <v>-4.914797906889934</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9095295310603362</v>
+        <v>1.021526674136894</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3474474713592783</v>
+        <v>-0.2736836069129659</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.779333778391049</v>
+        <v>2.823592097058836</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.254665591939021</v>
+        <v>-4.974672734247626</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8716170915186852</v>
+        <v>0.9836142345952434</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.3335584342706581</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.729446373377859</v>
+        <v>2.773704692045647</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.167866094160013</v>
+        <v>-4.887873236468618</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9287373839528548</v>
+        <v>1.040734527029413</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.3335584342706581</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.751846866700425</v>
+        <v>2.796105185368213</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.170335800621819</v>
+        <v>-4.890342942930424</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9278219027415444</v>
+        <v>1.039819045818102</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4097920051787766</v>
+        <v>-0.3360281407324642</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.750437444196754</v>
+        <v>2.794695762864541</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.238705986945829</v>
+        <v>-4.958713129254434</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9114807506866422</v>
+        <v>1.023477893763201</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.3267524416962493</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.767009786093185</v>
+        <v>2.811268104760972</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.117289557319353</v>
+        <v>-4.837296699627958</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9504840311691241</v>
+        <v>1.062481174245682</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.3267524416962493</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.757446494725076</v>
+        <v>2.801704813392863</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.148282716648058</v>
+        <v>-4.868289858956663</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7627963324780289</v>
+        <v>0.874793475554587</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.3267524416962493</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.582156059765463</v>
+        <v>2.62641437843325</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.972808456855589</v>
+        <v>-4.692815599164193</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8375532683868046</v>
+        <v>0.9495504114633626</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.3267524416962493</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.58672329175725</v>
+        <v>2.630981610425038</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.083744709496838</v>
+        <v>-4.803751851805442</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7689207960915119</v>
+        <v>0.8809179391680702</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.3267524416962493</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.562465320518458</v>
+        <v>2.606723639186245</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581295</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.286771287040071</v>
+        <v>-5.006778429348675</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6908415502941243</v>
+        <v>0.8028386933706824</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.5297790192394827</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.443780759212423</v>
+        <v>2.48803907788021</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734164</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.128845688104778</v>
+        <v>-4.848852830413382</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7641841763003741</v>
+        <v>0.8761813193769319</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.5297790192394827</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.453953145644555</v>
+        <v>2.498211464312343</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.277166941915906</v>
+        <v>-4.997174084224511</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.6998019453497828</v>
+        <v>0.8117990884263409</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.5297790192394827</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.448899416218416</v>
+        <v>2.493157734886203</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786048</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.278350026566967</v>
+        <v>-4.998357168875572</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.691104486933884</v>
+        <v>0.8031016300104421</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6091859321523065</v>
+        <v>-0.5354220677059942</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.437289362583035</v>
+        <v>2.481547681250822</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.155222319572884</v>
+        <v>-4.875229461881489</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7409074427646187</v>
+        <v>0.852904585841177</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6091859321523065</v>
+        <v>-0.5354220677059942</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.437841235616136</v>
+        <v>2.482099554283923</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.062411838122024</v>
+        <v>-4.782418980430629</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7073043272363284</v>
+        <v>0.8193014703128865</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5163754507014472</v>
+        <v>-0.4426115862551349</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.422800216378017</v>
+        <v>2.467058535045805</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.013848785900994</v>
+        <v>-4.733855928209599</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7286030240493413</v>
+        <v>0.8406001671258991</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.467812398480417</v>
+        <v>-0.3940485340341047</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.453811523635236</v>
+        <v>2.498069842303023</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.901177567664744</v>
+        <v>-4.621184709973349</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7687472198555643</v>
+        <v>0.8807443629321223</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3551411802441668</v>
+        <v>-0.2813773157978545</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.516489963088709</v>
+        <v>2.560748281756497</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.788800566482071</v>
+        <v>-4.508807708790676</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8191893161593007</v>
+        <v>0.9311864592358587</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3551411802441668</v>
+        <v>-0.2813773157978545</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.521981258919376</v>
+        <v>2.566239577587164</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.987035135368802</v>
+        <v>-4.707042277677407</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7513926903731474</v>
+        <v>0.8633898334497054</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5533757491308974</v>
+        <v>-0.479611884684585</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.414537719355877</v>
+        <v>2.458796038023665</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.070036416394081</v>
+        <v>-4.790043558702686</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5565478979636889</v>
+        <v>0.6685450410402471</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.4981827692117588</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.241750908640226</v>
+        <v>2.286009227308014</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199272</v>
+        <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.910842144337504</v>
+        <v>-4.630849286646109</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7403752675055253</v>
+        <v>0.8523724105820834</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.4981827692117588</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.361900569359432</v>
+        <v>2.406158888027219</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.997440727318607</v>
+        <v>-4.717447869627212</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7202488604154071</v>
+        <v>0.8322460034919652</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.4981827692117588</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.376413595461755</v>
+        <v>2.420671914129542</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383427</v>
+        <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.959057064760456</v>
+        <v>-4.679064207069061</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7330217667810364</v>
+        <v>0.8450189098575944</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.53356297109992</v>
+        <v>-0.4597991066536076</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.396863234339014</v>
+        <v>2.441121553006802</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002488</v>
+        <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.78194073472529</v>
+        <v>-4.501947877033895</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8005973276404046</v>
+        <v>0.9125944707169626</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.53356297109992</v>
+        <v>-0.4597991066536076</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.393592263184316</v>
+        <v>2.437850581852103</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263905</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.752238610748996</v>
+        <v>-4.472245753057601</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8131615689928351</v>
+        <v>0.9251587120693934</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5380330963152333</v>
+        <v>-0.464269231868921</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.391593579817041</v>
+        <v>2.435851898484829</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072580148124</v>
+        <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.572863189510229</v>
+        <v>-4.292870331818833</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8786987127947565</v>
+        <v>0.9906958558713148</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3812563381445147</v>
+        <v>-0.3074924736982023</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.479446610025887</v>
+        <v>2.523704928693674</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.489090507066867</v>
+        <v>3.837299870696064</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.512125274417783</v>
+        <v>-4.33788454533944</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8838013341633246</v>
+        <v>0.9534976257946619</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3009926357637203</v>
+        <v>-0.3378413690128069</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.508412286785953</v>
+        <v>2.486303046836501</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240509.xlsx
+++ b/tame_output/ON/bt/strategyON_20240509.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.5%</t>
+          <t>134.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.4%</t>
+          <t>-56.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.2%</t>
+          <t>443.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.4%</t>
+          <t>-607.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.9%</t>
+          <t>-285.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.8%</t>
+          <t>-257.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-197.4%</t>
+          <t>-164.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1958"/>
+  <dimension ref="A1:G1959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.646473517011048</v>
+        <v>-8.642414011937825</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3417836762955733</v>
+        <v>-0.3401598742662846</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.73618879205209</v>
+        <v>-1.731620191415415</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.07544887959134</v>
+        <v>2.078190039973345</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.079822625121283</v>
+        <v>-9.075763120048061</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5191496240740707</v>
+        <v>-0.5175258220447816</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.73618879205209</v>
+        <v>-1.731620191415415</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.071422575056936</v>
+        <v>2.074163735438941</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.462824013863914</v>
+        <v>-9.458764508790692</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6724522808927071</v>
+        <v>-0.6708284788634185</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.73618879205209</v>
+        <v>-1.731620191415415</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.071320473735352</v>
+        <v>2.074061634117357</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.620222894077035</v>
+        <v>-9.616163389003813</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7328403170065254</v>
+        <v>-0.7312165149772363</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.893587672265211</v>
+        <v>-1.889019071628536</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.97945266157891</v>
+        <v>1.982193821960915</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.979753216581036</v>
+        <v>-9.975693711507814</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8713021427100758</v>
+        <v>-0.8696783406807871</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.893587672265211</v>
+        <v>-1.889019071628536</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.98480296487696</v>
+        <v>1.987544125258965</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.30615324524605</v>
+        <v>-10.30209374017283</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9939461342189033</v>
+        <v>-0.9923223321896146</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.219987700930224</v>
+        <v>-2.215419100293549</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.79687896763513</v>
+        <v>1.799620128017135</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.52530221332025</v>
+        <v>-10.52124270824702</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.078563970826814</v>
+        <v>-1.076940168797524</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.439136669004421</v>
+        <v>-2.434568068367746</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.66843133741238</v>
+        <v>1.671172497794385</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.52161128836384</v>
+        <v>-10.51755178329061</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.077087600844249</v>
+        <v>-1.07546379881496</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.439136669004421</v>
+        <v>-2.434568068367746</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.66843133741238</v>
+        <v>1.671172497794385</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.7258694636937</v>
+        <v>-10.72180995862048</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.153277673857552</v>
+        <v>-1.151653871828263</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.56677561361841</v>
+        <v>-2.562207012981735</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.597361167762629</v>
+        <v>1.600102328144634</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.94390723532488</v>
+        <v>-10.93984773025166</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.236010228025588</v>
+        <v>-1.234386425996299</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.741546381714309</v>
+        <v>-2.736977781077634</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.496981261389526</v>
+        <v>1.499722421771531</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.87043740365743</v>
+        <v>-10.86637789858421</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.191250593865187</v>
+        <v>-1.189626791835898</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.668076550046861</v>
+        <v>-2.663507949410186</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.556434861883416</v>
+        <v>1.559176022265421</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.04556182104397</v>
+        <v>-11.04150231597075</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.246745140072287</v>
+        <v>-1.245121338042998</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.843200967433404</v>
+        <v>-2.838632366796729</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.465915432199006</v>
+        <v>1.468656592581011</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.28001391505846</v>
+        <v>-11.27595440998524</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.347745142579679</v>
+        <v>-1.34612134055039</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.843200967433404</v>
+        <v>-2.838632366796729</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.45869626729741</v>
+        <v>1.461437427679415</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.5678177595957</v>
+        <v>-11.56375825452248</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.469538871168551</v>
+        <v>-1.467915069139262</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.131004811970643</v>
+        <v>-3.126436211333968</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.279341769801091</v>
+        <v>1.282082930183096</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.79764220675952</v>
+        <v>-11.7935827016863</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.560352860195525</v>
+        <v>-1.558729058166236</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.293652349040803</v>
+        <v>-3.289083748404128</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.182869037397551</v>
+        <v>1.185610197779556</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.02967112649579</v>
+        <v>-12.02561162142256</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.650470699460915</v>
+        <v>-1.648846897431626</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.355665046229226</v>
+        <v>-3.351096445592551</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.148355147713612</v>
+        <v>1.151096308095617</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.97765561252697</v>
+        <v>-11.97359610745375</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.625674158186988</v>
+        <v>-1.624050356157699</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.355665046229226</v>
+        <v>-3.351096445592551</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.152345483400013</v>
+        <v>1.155086643782018</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.11932745425109</v>
+        <v>-12.11526794917787</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.683818121775379</v>
+        <v>-1.682194319746089</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.355665046229226</v>
+        <v>-3.351096445592551</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.150870256501271</v>
+        <v>1.153611416883276</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.06973660982626</v>
+        <v>-12.06567710475304</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.648928373840572</v>
+        <v>-1.647304571811283</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.306074201804392</v>
+        <v>-3.301505601167718</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.195678173321044</v>
+        <v>1.198419333703049</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.87058450258916</v>
+        <v>-11.86652499751594</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.582318664592415</v>
+        <v>-1.580694862563127</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.140751675854579</v>
+        <v>-3.136183075217904</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.281820555244249</v>
+        <v>1.284561715626254</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.64473934986975</v>
+        <v>-11.64067984479653</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.482401530468442</v>
+        <v>-1.480777728439154</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.098825000267416</v>
+        <v>-3.094256399630741</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.316555633632756</v>
+        <v>1.319296794014761</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.52016069353216</v>
+        <v>-11.51610118845893</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.431430923377346</v>
+        <v>-1.429807121348058</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.098825000267416</v>
+        <v>-3.094256399630741</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.317694778188815</v>
+        <v>1.32043593857082</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.57305598157644</v>
+        <v>-11.56899647650322</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.449955264432954</v>
+        <v>-1.448331462403664</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.093869654178969</v>
+        <v>-3.089301053542294</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.32330176000399</v>
+        <v>1.326042920385995</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.28914725064769</v>
+        <v>-11.28508774557447</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.330658067822817</v>
+        <v>-1.329034265793529</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.093869654178969</v>
+        <v>-3.089301053542294</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.329035464242626</v>
+        <v>1.331776624624631</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.21778085803805</v>
+        <v>-11.21372135296482</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.311848773172824</v>
+        <v>-1.310224971143535</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.022503261569322</v>
+        <v>-3.017934660932646</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.36211803741455</v>
+        <v>1.364859197796555</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.95394399083398</v>
+        <v>-10.94988448576076</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.216197507604103</v>
+        <v>-1.214573705574815</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.022503261569322</v>
+        <v>-3.017934660932646</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.352234556101642</v>
+        <v>1.354975716483648</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.68670218996558</v>
+        <v>-10.68264268489236</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.111135347756118</v>
+        <v>-1.109511545726829</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.022503261569322</v>
+        <v>-3.017934660932646</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.350399995602269</v>
+        <v>1.353141155984274</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.58879515128909</v>
+        <v>-10.58473564621587</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.072272847258982</v>
+        <v>-1.070649045229694</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.954517511708765</v>
+        <v>-2.94994891107209</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.390891130545141</v>
+        <v>1.393632290927147</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.56484161031313</v>
+        <v>-10.56078210523991</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.062022924723105</v>
+        <v>-1.060399122693817</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.930563970732808</v>
+        <v>-2.925995370096132</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.40593176127621</v>
+        <v>1.408672921658215</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.30078167199033</v>
+        <v>-10.29672216691711</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9696592655557392</v>
+        <v>-0.9680354635264505</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.666504032410012</v>
+        <v>-2.661935431773336</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.551107408108135</v>
+        <v>1.55384856849014</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.593702048485497</v>
+        <v>-9.710963191749034</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6896144498141052</v>
+        <v>-0.7365189071195202</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.666504032410012</v>
+        <v>-2.661935431773336</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.548320374447834</v>
+        <v>1.55106153482984</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.553517750119306</v>
+        <v>-9.670778893382844</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6731971065797877</v>
+        <v>-0.7201015638852026</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.626319734043821</v>
+        <v>-2.621751133407145</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.57277457735539</v>
+        <v>1.575515737737395</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.473447954581502</v>
+        <v>-9.590709097845039</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6418023671439088</v>
+        <v>-0.6887068244493237</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.546249938506017</v>
+        <v>-2.541681337869341</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.620183275898829</v>
+        <v>1.622924436280835</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.239966732351903</v>
+        <v>-9.35722787561544</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5404854494142168</v>
+        <v>-0.5873899067196318</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.312768716276418</v>
+        <v>-2.308200115639743</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.768196438074441</v>
+        <v>1.770937598456446</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.060258202208029</v>
+        <v>-9.177519345471566</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4714942476696264</v>
+        <v>-0.5183987049750414</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.255597212113722</v>
+        <v>-2.251028611477047</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.799607130259099</v>
+        <v>1.802348290641105</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.927982728577142</v>
+        <v>-9.045243871840679</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4232165714702445</v>
+        <v>-0.4701210287756594</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.123321738482836</v>
+        <v>-2.118753137846161</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.874339901184658</v>
+        <v>1.877081061566664</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.737383053903988</v>
+        <v>-8.854644197167525</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3441616409133466</v>
+        <v>-0.3910660982187615</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.932722063809683</v>
+        <v>-1.928153463173008</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.991514766676187</v>
+        <v>1.994255927058192</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.488383255220407</v>
+        <v>-8.605644398483944</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2316553802162553</v>
+        <v>-0.2785598375216702</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.932722063809683</v>
+        <v>-1.928153463173008</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.004421107899845</v>
+        <v>2.007162268281851</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.593973244993512</v>
+        <v>-8.711234388257049</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.401867305724716</v>
+        <v>-0.4487717630301304</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.038312053582787</v>
+        <v>-2.033743452946112</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.813091184436764</v>
+        <v>1.815832344818769</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.612708147112109</v>
+        <v>-8.729969290375646</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3608169246950683</v>
+        <v>-0.4077213820004832</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.038312053582787</v>
+        <v>-2.033743452946112</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.86163552631385</v>
+        <v>1.864376686695856</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.464768105704509</v>
+        <v>-8.582029248968047</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4215198308201962</v>
+        <v>-0.4684242881256111</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.01799113767423</v>
+        <v>-2.013422537037555</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.753949153170817</v>
+        <v>1.756690313552822</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.440539469315537</v>
+        <v>-8.557800612579074</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4205423625180851</v>
+        <v>-0.4674468198235</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.993762501285258</v>
+        <v>-1.989193900648583</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.759772348750722</v>
+        <v>1.762513509132728</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.396991062544846</v>
+        <v>-8.514252205808383</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4100836119049021</v>
+        <v>-0.4569880692103165</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.993762501285258</v>
+        <v>-1.989193900648583</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.752811736655629</v>
+        <v>1.755552897037634</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.154842669090987</v>
+        <v>-8.272103812354525</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2987619001422157</v>
+        <v>-0.3456663574476302</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.993762501285258</v>
+        <v>-1.989193900648583</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.767274091036772</v>
+        <v>1.770015251418777</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.09161329732264</v>
+        <v>-8.208874440586177</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2789380309756817</v>
+        <v>-0.3258424882810962</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.993762501285258</v>
+        <v>-1.989193900648583</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.761806211495967</v>
+        <v>1.764547371877973</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.968322162505509</v>
+        <v>-8.085583305769047</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2321234830382521</v>
+        <v>-0.2790279403436675</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.870471366468128</v>
+        <v>-1.865902765831452</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.833278986396822</v>
+        <v>1.836020146778828</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.947172963602066</v>
+        <v>-8.064434106865605</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2159628252395498</v>
+        <v>-0.2628672825449652</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.849322167564684</v>
+        <v>-1.844753566928009</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.853669483976214</v>
+        <v>1.856410644358219</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.703407521618622</v>
+        <v>-7.82066866488216</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1226759400991213</v>
+        <v>-0.1695803974045371</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.849322167564684</v>
+        <v>-1.844753566928009</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.849450192323264</v>
+        <v>1.85219135270527</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.439379454425362</v>
+        <v>-7.556640597688901</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.01494039930180158</v>
+        <v>-0.06184485660721695</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.647456768748731</v>
+        <v>-1.642888168112055</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.972693745532852</v>
+        <v>1.975434905914858</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.189529060476287</v>
+        <v>-7.306790203739826</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0777418332615305</v>
+        <v>0.03083737595611469</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.647456768748731</v>
+        <v>-1.642888168112055</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.965435820516555</v>
+        <v>1.96817698089856</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.013636968008855</v>
+        <v>-7.130898111272394</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1516977937691522</v>
+        <v>0.1047933364637363</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.647456768748731</v>
+        <v>-1.642888168112055</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.969034944037203</v>
+        <v>1.971776104419209</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.842190504986392</v>
+        <v>-6.959451648249931</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2336038850326911</v>
+        <v>0.1866994277272753</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.476010305726267</v>
+        <v>-1.471441705089592</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.085230327905235</v>
+        <v>2.08797148828724</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.617157505317569</v>
+        <v>-6.734418648581108</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3226375625165172</v>
+        <v>0.2757331052111018</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.250977306057445</v>
+        <v>-1.246408705420769</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.219270605322825</v>
+        <v>2.222011765704831</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.402523127681162</v>
+        <v>-6.519784270944701</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4131861146253972</v>
+        <v>0.3662816573199819</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.036342928421038</v>
+        <v>-1.031774327784362</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.352746032958987</v>
+        <v>2.355487193340992</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.309523086475264</v>
+        <v>-6.426784229738803</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4315803898915522</v>
+        <v>0.3846759325861364</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.036342928421038</v>
+        <v>-1.031774327784362</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.333940291742783</v>
+        <v>2.336681452124788</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.069092589670404</v>
+        <v>-6.186353732933942</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5294956652383735</v>
+        <v>0.4825912079329582</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7959124316161774</v>
+        <v>-0.791343830979502</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.479941666450576</v>
+        <v>2.482682826832582</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.996850021499209</v>
+        <v>-6.114111164762748</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5623220063416716</v>
+        <v>0.5154175490362563</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7959124316161774</v>
+        <v>-0.791343830979502</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.483870980285396</v>
+        <v>2.486612140667402</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.880910171874024</v>
+        <v>-5.998171315137562</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6093765301090861</v>
+        <v>0.5624720728036703</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7190907006000535</v>
+        <v>-0.7145220999633781</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.530642602812411</v>
+        <v>2.533383763194416</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.638254583450861</v>
+        <v>-5.7555157267144</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7034368366983443</v>
+        <v>0.656532379392929</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7190907006000535</v>
+        <v>-0.7145220999633781</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.527640674032404</v>
+        <v>2.530381834414409</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.41823378541385</v>
+        <v>-5.535494928677389</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7930241929237627</v>
+        <v>0.7461197356183473</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5778708555320733</v>
+        <v>-0.5733022548953979</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.613951618083806</v>
+        <v>2.616692778465812</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009951</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.218985155509041</v>
+        <v>-5.33624629877258</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8886178276875096</v>
+        <v>0.8417133703820943</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5778708555320733</v>
+        <v>-0.5733022548953979</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.62984580088563</v>
+        <v>2.632586961267635</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.059470051989671</v>
+        <v>-5.17673119525321</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9535697135355594</v>
+        <v>0.906665256230144</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4183557520127034</v>
+        <v>-0.413787151376028</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.726700707437554</v>
+        <v>2.729441867819559</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.914797906889934</v>
+        <v>-5.032059050153473</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.021526674136894</v>
+        <v>0.9746222168314791</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2736836069129659</v>
+        <v>-0.2691150062762905</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.823592097058836</v>
+        <v>2.826333257440841</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.974672734247626</v>
+        <v>-5.091933877511165</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9836142345952434</v>
+        <v>0.9367097772898276</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3335584342706581</v>
+        <v>-0.3289898336339827</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.773704692045647</v>
+        <v>2.776445852427652</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.887873236468618</v>
+        <v>-5.005134379732157</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.040734527029413</v>
+        <v>0.9938300697239972</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3335584342706581</v>
+        <v>-0.3289898336339827</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.796105185368213</v>
+        <v>2.798846345750218</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.890342942930424</v>
+        <v>-5.007604086193963</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.039819045818102</v>
+        <v>0.9929145885126869</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3360281407324642</v>
+        <v>-0.3314595400957888</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.794695762864541</v>
+        <v>2.797436923246546</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.958713129254434</v>
+        <v>-5.075974272517973</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.023477893763201</v>
+        <v>0.9765734364577847</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3267524416962493</v>
+        <v>-0.3221838410595739</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.811268104760972</v>
+        <v>2.814009265142977</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.837296699627958</v>
+        <v>-4.954557842891496</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.062481174245682</v>
+        <v>1.015576716940267</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3267524416962493</v>
+        <v>-0.3221838410595739</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.801704813392863</v>
+        <v>2.804445973774869</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.868289858956663</v>
+        <v>-4.985551002220202</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.874793475554587</v>
+        <v>0.8278890182491714</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3267524416962493</v>
+        <v>-0.3221838410595739</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.62641437843325</v>
+        <v>2.629155538815255</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675903</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.692815599164193</v>
+        <v>-4.810076742427732</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9495504114633626</v>
+        <v>0.902645954157947</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3267524416962493</v>
+        <v>-0.3221838410595739</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.630981610425038</v>
+        <v>2.633722770807043</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.803751851805442</v>
+        <v>-4.921012995068981</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8809179391680702</v>
+        <v>0.8340134818626546</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3267524416962493</v>
+        <v>-0.3221838410595739</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.606723639186245</v>
+        <v>2.60946479956825</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.006778429348675</v>
+        <v>-5.124039572612214</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8028386933706824</v>
+        <v>0.7559342360652668</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5297790192394827</v>
+        <v>-0.5252104186028073</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.48803907788021</v>
+        <v>2.490780238262216</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.848852830413382</v>
+        <v>-4.966113973676921</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8761813193769319</v>
+        <v>0.8292768620715165</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5297790192394827</v>
+        <v>-0.5252104186028073</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.498211464312343</v>
+        <v>2.500952624694348</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.997174084224511</v>
+        <v>-5.11443522748805</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8117990884263409</v>
+        <v>0.7648946311209253</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5297790192394827</v>
+        <v>-0.5252104186028073</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.493157734886203</v>
+        <v>2.495898895268208</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.998357168875572</v>
+        <v>-5.115618312139111</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8031016300104421</v>
+        <v>0.7561971727050265</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5354220677059942</v>
+        <v>-0.5308534670693188</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.481547681250822</v>
+        <v>2.484288841632827</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.875229461881489</v>
+        <v>-4.992490605145028</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.852904585841177</v>
+        <v>0.8060001285357614</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5354220677059942</v>
+        <v>-0.5308534670693188</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.482099554283923</v>
+        <v>2.484840714665929</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.782418980430629</v>
+        <v>-4.899680123694168</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8193014703128865</v>
+        <v>0.7723970130074709</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4426115862551349</v>
+        <v>-0.4380429856184594</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.467058535045805</v>
+        <v>2.46979969542781</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.733855928209599</v>
+        <v>-4.851117071473138</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8406001671258991</v>
+        <v>0.7936957098204838</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3940485340341047</v>
+        <v>-0.3894799333974293</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.498069842303023</v>
+        <v>2.500811002685029</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.621184709973349</v>
+        <v>-4.738445853236888</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8807443629321223</v>
+        <v>0.8338399056267067</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2813773157978545</v>
+        <v>-0.2768087151611791</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.560748281756497</v>
+        <v>2.563489442138502</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.508807708790676</v>
+        <v>-4.626068852054215</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9311864592358587</v>
+        <v>0.8842820019304432</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2813773157978545</v>
+        <v>-0.2768087151611791</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.566239577587164</v>
+        <v>2.568980737969169</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.707042277677407</v>
+        <v>-4.824303420940946</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8633898334497054</v>
+        <v>0.8164853761442898</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.479611884684585</v>
+        <v>-0.4750432840479096</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.458796038023665</v>
+        <v>2.46153719840567</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.790043558702686</v>
+        <v>-4.907304701966225</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6685450410402471</v>
+        <v>0.6216405837348316</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4981827692117588</v>
+        <v>-0.4936141685750834</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.286009227308014</v>
+        <v>2.288750387690019</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271273519927</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.630849286646109</v>
+        <v>-4.748110429909648</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8523724105820834</v>
+        <v>0.805467953276668</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4981827692117588</v>
+        <v>-0.4936141685750834</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.406158888027219</v>
+        <v>2.408900048409225</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566077</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.717447869627212</v>
+        <v>-4.834709012890751</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8322460034919652</v>
+        <v>0.7853415461865496</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4981827692117588</v>
+        <v>-0.4936141685750834</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.420671914129542</v>
+        <v>2.423413074511548</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383425</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.679064207069061</v>
+        <v>-4.7963253503326</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8450189098575944</v>
+        <v>0.7981144525521788</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4597991066536076</v>
+        <v>-0.4552305060169322</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.441121553006802</v>
+        <v>2.443862713388807</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.501947877033895</v>
+        <v>-4.619209020297434</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9125944707169626</v>
+        <v>0.8656900134115473</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4597991066536076</v>
+        <v>-0.4552305060169322</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.437850581852103</v>
+        <v>2.440591742234109</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.472245753057601</v>
+        <v>-4.58950689632114</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9251587120693934</v>
+        <v>0.8782542547639778</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.464269231868921</v>
+        <v>-0.4597006312322456</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.435851898484829</v>
+        <v>2.438593058866834</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.75072580148124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.292870331818833</v>
+        <v>-4.410131475082372</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9906958558713148</v>
+        <v>0.9437913985658992</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3074924736982023</v>
+        <v>-0.3029238730615269</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.523704928693674</v>
+        <v>2.52644608907568</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,45 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.837299870696064</v>
+        <v>3.716988143452236</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.33788454533944</v>
+        <v>-4.455145688602979</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9534976257946619</v>
+        <v>0.9065931684892463</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3378413690128069</v>
+        <v>-0.3332727683761315</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.486303046836501</v>
+        <v>2.489044207218507</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="2" t="n">
+        <v>45421</v>
+      </c>
+      <c r="B1959" t="n">
+        <v>3.841500630401089</v>
+      </c>
+      <c r="C1959" t="n">
+        <v>2.826111852614932</v>
+      </c>
+      <c r="D1959" t="n">
+        <v>-4.455145688602979</v>
+      </c>
+      <c r="E1959" t="n">
+        <v>0.9065931684892463</v>
+      </c>
+      <c r="F1959" t="n">
+        <v>-0.3332727683761315</v>
+      </c>
+      <c r="G1959" t="n">
+        <v>2.8191756496013</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240509.xlsx
+++ b/tame_output/ON/bt/strategyON_20240509.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>114.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.4%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.3%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>443.9%</t>
+          <t>440.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.1%</t>
+          <t>-620.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.0%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-285.6%</t>
+          <t>-290.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-155.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.3%</t>
+          <t>-265.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.1%</t>
+          <t>-190.8%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.642414011937825</v>
+        <v>-8.805145726365682</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3401598742662846</v>
+        <v>-0.405252560037427</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.731620191415415</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.078190039973345</v>
+        <v>2.031190560923552</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.075763120048061</v>
+        <v>-9.238494834475917</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5175258220447816</v>
+        <v>-0.5826185078159245</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.731620191415415</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.074163735438941</v>
+        <v>2.027164256389149</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.458764508790692</v>
+        <v>-9.621496223218548</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6708284788634185</v>
+        <v>-0.7359211646345609</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.731620191415415</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.074061634117357</v>
+        <v>2.027062155067564</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.616163389003813</v>
+        <v>-9.778895103431669</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7312165149772363</v>
+        <v>-0.7963092007483792</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.889019071628536</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.982193821960915</v>
+        <v>1.935194342911122</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.975693711507814</v>
+        <v>-10.13842542593567</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8696783406807871</v>
+        <v>-0.9347710264519291</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.889019071628536</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.987544125258965</v>
+        <v>1.940544646209172</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.30209374017283</v>
+        <v>-10.46482545460068</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9923223321896146</v>
+        <v>-1.057415017960758</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.215419100293549</v>
+        <v>-2.293751565376537</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.799620128017135</v>
+        <v>1.752620648967342</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.52124270824702</v>
+        <v>-10.68397442267488</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.076940168797524</v>
+        <v>-1.142032854568667</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.434568068367746</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.671172497794385</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.51755178329061</v>
+        <v>-10.68028349771847</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.07546379881496</v>
+        <v>-1.140556484586103</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.434568068367746</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.671172497794385</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.72180995862048</v>
+        <v>-10.88454167304833</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.151653871828263</v>
+        <v>-1.216746557599406</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.562207012981735</v>
+        <v>-2.640539478064723</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.600102328144634</v>
+        <v>1.553102849094841</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.93984773025166</v>
+        <v>-11.10257944467951</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.234386425996299</v>
+        <v>-1.299479111767441</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.736977781077634</v>
+        <v>-2.815310246160622</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.499722421771531</v>
+        <v>1.452722942721738</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.86637789858421</v>
+        <v>-11.02910961301206</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.189626791835898</v>
+        <v>-1.254719477607041</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.663507949410186</v>
+        <v>-2.741840414493173</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.559176022265421</v>
+        <v>1.512176543215628</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.04150231597075</v>
+        <v>-11.20423403039861</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.245121338042998</v>
+        <v>-1.310214023814141</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.838632366796729</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.468656592581011</v>
+        <v>1.421657113531219</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.27595440998524</v>
+        <v>-11.4386861244131</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.34612134055039</v>
+        <v>-1.411214026321533</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.838632366796729</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.461437427679415</v>
+        <v>1.414437948629623</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.56375825452248</v>
+        <v>-11.72648996895033</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.467915069139262</v>
+        <v>-1.533007754910404</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.126436211333968</v>
+        <v>-3.204768676416955</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.282082930183096</v>
+        <v>1.235083451133304</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.7935827016863</v>
+        <v>-11.95631441611416</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.558729058166236</v>
+        <v>-1.623821743937378</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.289083748404128</v>
+        <v>-3.367416213487116</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.185610197779556</v>
+        <v>1.138610718729764</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.02561162142256</v>
+        <v>-12.18834333585042</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.648846897431626</v>
+        <v>-1.713939583202768</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.351096445592551</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.151096308095617</v>
+        <v>1.104096829045825</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.97359610745375</v>
+        <v>-12.13632782188161</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.624050356157699</v>
+        <v>-1.689143041928842</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.351096445592551</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.155086643782018</v>
+        <v>1.108087164732225</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.11526794917787</v>
+        <v>-12.27799966360573</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.682194319746089</v>
+        <v>-1.747287005517232</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.351096445592551</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.153611416883276</v>
+        <v>1.106611937833484</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.06567710475304</v>
+        <v>-12.22840881918089</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.647304571811283</v>
+        <v>-1.712397257582426</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.301505601167718</v>
+        <v>-3.379838066250705</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.198419333703049</v>
+        <v>1.151419854653256</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.86652499751594</v>
+        <v>-12.02925671194379</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.580694862563127</v>
+        <v>-1.645787548334269</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.136183075217904</v>
+        <v>-3.214515540300892</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.284561715626254</v>
+        <v>1.237562236576461</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.64067984479653</v>
+        <v>-11.80341155922438</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.480777728439154</v>
+        <v>-1.545870414210296</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.094256399630741</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.319296794014761</v>
+        <v>1.272297314964968</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.51610118845893</v>
+        <v>-11.67883290288679</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.429807121348058</v>
+        <v>-1.494899807119201</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.094256399630741</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.32043593857082</v>
+        <v>1.273436459521027</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.56899647650322</v>
+        <v>-11.73172819093108</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.448331462403664</v>
+        <v>-1.513424148174807</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.089301053542294</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.326042920385995</v>
+        <v>1.279043441336202</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.28508774557447</v>
+        <v>-11.44781946000233</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.329034265793529</v>
+        <v>-1.394126951564671</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.089301053542294</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.331776624624631</v>
+        <v>1.284777145574839</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.21372135296482</v>
+        <v>-11.37645306739268</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.310224971143535</v>
+        <v>-1.375317656914677</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.017934660932646</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.364859197796555</v>
+        <v>1.317859718746762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.94988448576076</v>
+        <v>-11.11261620018861</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.214573705574815</v>
+        <v>-1.279666391345957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.017934660932646</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.354975716483648</v>
+        <v>1.307976237433855</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.68264268489236</v>
+        <v>-10.84537439932021</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.109511545726829</v>
+        <v>-1.174604231497972</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.017934660932646</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.353141155984274</v>
+        <v>1.306141676934481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.58473564621587</v>
+        <v>-10.74746736064372</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.070649045229694</v>
+        <v>-1.135741731000837</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.94994891107209</v>
+        <v>-3.028281376155078</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.393632290927147</v>
+        <v>1.346632811877354</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.56078210523991</v>
+        <v>-10.72351381966777</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.060399122693817</v>
+        <v>-1.12549180846496</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.925995370096132</v>
+        <v>-3.00432783517912</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.408672921658215</v>
+        <v>1.361673442608422</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.29672216691711</v>
+        <v>-10.45945388134497</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9680354635264505</v>
+        <v>-1.033128149297593</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.661935431773336</v>
+        <v>-2.740267896856324</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.55384856849014</v>
+        <v>1.506849089440348</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.710963191749034</v>
+        <v>-9.752374257840131</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7365189071195202</v>
+        <v>-0.753083333555959</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.661935431773336</v>
+        <v>-2.740267896856324</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.55106153482984</v>
+        <v>1.504062055780047</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.670778893382844</v>
+        <v>-9.712189959473941</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7201015638852026</v>
+        <v>-0.7366659903216415</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.621751133407145</v>
+        <v>-2.700083598490133</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.575515737737395</v>
+        <v>1.528516258687603</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.590709097845039</v>
+        <v>-9.632120163936136</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6887068244493237</v>
+        <v>-0.7052712508857626</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.541681337869341</v>
+        <v>-2.620013802952329</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.622924436280835</v>
+        <v>1.575924957231042</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.35722787561544</v>
+        <v>-9.398638941706537</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5873899067196318</v>
+        <v>-0.6039543331560706</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.308200115639743</v>
+        <v>-2.386532580722731</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.770937598456446</v>
+        <v>1.723938119406654</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.177519345471566</v>
+        <v>-9.218930411562663</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5183987049750414</v>
+        <v>-0.5349631314114802</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.251028611477047</v>
+        <v>-2.329361076560035</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.802348290641105</v>
+        <v>1.755348811591312</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.045243871840679</v>
+        <v>-9.086654937931776</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4701210287756594</v>
+        <v>-0.4866854552120983</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.118753137846161</v>
+        <v>-2.197085602929148</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.877081061566664</v>
+        <v>1.830081582516871</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.854644197167525</v>
+        <v>-8.896055263258623</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3910660982187615</v>
+        <v>-0.4076305246552003</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.928153463173008</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.994255927058192</v>
+        <v>1.947256448008399</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.605644398483944</v>
+        <v>-8.647055464575041</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2785598375216702</v>
+        <v>-0.2951242639581091</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.928153463173008</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.007162268281851</v>
+        <v>1.960162789232058</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.711234388257049</v>
+        <v>-8.752645454348146</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4487717630301304</v>
+        <v>-0.4653361894665693</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.033743452946112</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.815832344818769</v>
+        <v>1.768832865768977</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.729969290375646</v>
+        <v>-8.771380356466743</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4077213820004832</v>
+        <v>-0.4242858084369221</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.033743452946112</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.864376686695856</v>
+        <v>1.817377207646063</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.582029248968047</v>
+        <v>-8.623440315059144</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4684242881256111</v>
+        <v>-0.4849887145620499</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.013422537037555</v>
+        <v>-2.091755002120542</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.756690313552822</v>
+        <v>1.70969083450303</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.557800612579074</v>
+        <v>-8.599211678670171</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4674468198235</v>
+        <v>-0.4840112462599389</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.989193900648583</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.762513509132728</v>
+        <v>1.715514030082935</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.514252205808383</v>
+        <v>-8.55566327189948</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4569880692103165</v>
+        <v>-0.4735524956467554</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.989193900648583</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.755552897037634</v>
+        <v>1.708553417987842</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.272103812354525</v>
+        <v>-8.313514878445622</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3456663574476302</v>
+        <v>-0.362230783884069</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.989193900648583</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.770015251418777</v>
+        <v>1.723015772368985</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.208874440586177</v>
+        <v>-8.250285506677274</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3258424882810962</v>
+        <v>-0.342406914717535</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.989193900648583</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.764547371877973</v>
+        <v>1.71754789282818</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.085583305769047</v>
+        <v>-8.126994371860144</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2790279403436675</v>
+        <v>-0.2955923667801064</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.865902765831452</v>
+        <v>-1.94423523091444</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.836020146778828</v>
+        <v>1.789020667729035</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.064434106865605</v>
+        <v>-8.105845172956702</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2628672825449652</v>
+        <v>-0.279431708981404</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.844753566928009</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.856410644358219</v>
+        <v>1.809411165308426</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.82066866488216</v>
+        <v>-7.862079730973258</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1695803974045371</v>
+        <v>-0.186144823840976</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.844753566928009</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.85219135270527</v>
+        <v>1.805191873655477</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.556640597688901</v>
+        <v>-7.598051663779998</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.06184485660721695</v>
+        <v>-0.0784092830436558</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.642888168112055</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.975434905914858</v>
+        <v>1.928435426865065</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.306790203739826</v>
+        <v>-7.348201269830923</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.03083737595611469</v>
+        <v>0.01427294951967584</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.642888168112055</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96817698089856</v>
+        <v>1.921177501848767</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.130898111272394</v>
+        <v>-7.172309177363491</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1047933364637363</v>
+        <v>0.08822891002729749</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.642888168112055</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.971776104419209</v>
+        <v>1.924776625369416</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.959451648249931</v>
+        <v>-7.000862714341028</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1866994277272753</v>
+        <v>0.1701350012908365</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.471441705089592</v>
+        <v>-1.54977417017258</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.08797148828724</v>
+        <v>2.040972009237448</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.734418648581108</v>
+        <v>-6.775829714672205</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2757331052111018</v>
+        <v>0.259168678774663</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.246408705420769</v>
+        <v>-1.324741170503757</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.222011765704831</v>
+        <v>2.175012286655038</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.519784270944701</v>
+        <v>-6.561195337035798</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3662816573199819</v>
+        <v>0.349717230883543</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.031774327784362</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.355487193340992</v>
+        <v>2.3084877142912</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.426784229738803</v>
+        <v>-6.4681952958299</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3846759325861364</v>
+        <v>0.3681115061496976</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.031774327784362</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.336681452124788</v>
+        <v>2.289681973074996</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.186353732933942</v>
+        <v>-6.22776479902504</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4825912079329582</v>
+        <v>0.4660267814965193</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.791343830979502</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.482682826832582</v>
+        <v>2.435683347782789</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.114111164762748</v>
+        <v>-6.155522230853845</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5154175490362563</v>
+        <v>0.4988531225998174</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.791343830979502</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.486612140667402</v>
+        <v>2.439612661617609</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.998171315137562</v>
+        <v>-6.03958238122866</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5624720728036703</v>
+        <v>0.5459076463672314</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7145220999633781</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.533383763194416</v>
+        <v>2.486384284144624</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.7555157267144</v>
+        <v>-5.884926612365134</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.656532379392929</v>
+        <v>0.6047680251326355</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7145220999633781</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.530381834414409</v>
+        <v>2.483382355364617</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.535494928677389</v>
+        <v>-5.664905814328123</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7461197356183473</v>
+        <v>0.6943553813580539</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5733022548953979</v>
+        <v>-0.6516347199783856</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.616692778465812</v>
+        <v>2.569693299416019</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.33624629877258</v>
+        <v>-5.465657184423314</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8417133703820943</v>
+        <v>0.7899490161218008</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5733022548953979</v>
+        <v>-0.6516347199783856</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.632586961267635</v>
+        <v>2.585587482217842</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.17673119525321</v>
+        <v>-5.306142080903944</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.906665256230144</v>
+        <v>0.8549009019698506</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.413787151376028</v>
+        <v>-0.4921196164590157</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.729441867819559</v>
+        <v>2.682442388769766</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.032059050153473</v>
+        <v>-5.161469935804207</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9746222168314791</v>
+        <v>0.9228578625711852</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2691150062762905</v>
+        <v>-0.3474474713592783</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.826333257440841</v>
+        <v>2.779333778391049</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.091933877511165</v>
+        <v>-5.221344763161899</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9367097772898276</v>
+        <v>0.8849454230295342</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3289898336339827</v>
+        <v>-0.4073222987169704</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.776445852427652</v>
+        <v>2.729446373377859</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.005134379732157</v>
+        <v>-5.13454526538289</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9938300697239972</v>
+        <v>0.9420657154637038</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3289898336339827</v>
+        <v>-0.4073222987169704</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.798846345750218</v>
+        <v>2.751846866700425</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.007604086193963</v>
+        <v>-5.137014971844696</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9929145885126869</v>
+        <v>0.9411502342523939</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3314595400957888</v>
+        <v>-0.4097920051787766</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.797436923246546</v>
+        <v>2.750437444196754</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.075974272517973</v>
+        <v>-5.205385158168706</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9765734364577847</v>
+        <v>0.9248090821974917</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3221838410595739</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.814009265142977</v>
+        <v>2.767009786093185</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.954557842891496</v>
+        <v>-5.08396872854223</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.015576716940267</v>
+        <v>0.9638123626799735</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3221838410595739</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.804445973774869</v>
+        <v>2.757446494725076</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.985551002220202</v>
+        <v>-5.114961887870935</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8278890182491714</v>
+        <v>0.7761246639888784</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3221838410595739</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.629155538815255</v>
+        <v>2.582156059765463</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.810076742427732</v>
+        <v>-4.939487628078465</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.902645954157947</v>
+        <v>0.8508815998976538</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3221838410595739</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.633722770807043</v>
+        <v>2.58672329175725</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.921012995068981</v>
+        <v>-5.050423880719714</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8340134818626546</v>
+        <v>0.7822491276023613</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3221838410595739</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.60946479956825</v>
+        <v>2.562465320518458</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.124039572612214</v>
+        <v>-5.253450458262948</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7559342360652668</v>
+        <v>0.7041698818049738</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5252104186028073</v>
+        <v>-0.603542883685795</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.490780238262216</v>
+        <v>2.443780759212423</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.966113973676921</v>
+        <v>-5.095524859327655</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8292768620715165</v>
+        <v>0.7775125078112231</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5252104186028073</v>
+        <v>-0.603542883685795</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.500952624694348</v>
+        <v>2.453953145644555</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.11443522748805</v>
+        <v>-5.243846113138783</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7648946311209253</v>
+        <v>0.7131302768606318</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5252104186028073</v>
+        <v>-0.603542883685795</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.495898895268208</v>
+        <v>2.448899416218416</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.115618312139111</v>
+        <v>-5.245029197789844</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7561971727050265</v>
+        <v>0.7044328184447335</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5308534670693188</v>
+        <v>-0.6091859321523065</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.484288841632827</v>
+        <v>2.437289362583035</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.992490605145028</v>
+        <v>-5.121901490795761</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8060001285357614</v>
+        <v>0.7542357742754682</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5308534670693188</v>
+        <v>-0.6091859321523065</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.484840714665929</v>
+        <v>2.437841235616136</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.899680123694168</v>
+        <v>-5.029091009344901</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7723970130074709</v>
+        <v>0.7206326587471774</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4380429856184594</v>
+        <v>-0.5163754507014472</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.46979969542781</v>
+        <v>2.422800216378017</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.851117071473138</v>
+        <v>-4.980527957123871</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7936957098204838</v>
+        <v>0.7419313555601903</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3894799333974293</v>
+        <v>-0.467812398480417</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.500811002685029</v>
+        <v>2.453811523635236</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.738445853236888</v>
+        <v>-4.867856738887621</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8338399056267067</v>
+        <v>0.7820755513664135</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2768087151611791</v>
+        <v>-0.3551411802441668</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.563489442138502</v>
+        <v>2.516489963088709</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.626068852054215</v>
+        <v>-4.755479737704948</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8842820019304432</v>
+        <v>0.8325176476701499</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2768087151611791</v>
+        <v>-0.3551411802441668</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.568980737969169</v>
+        <v>2.521981258919376</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.824303420940946</v>
+        <v>-4.953714306591679</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8164853761442898</v>
+        <v>0.7647210218839966</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4750432840479096</v>
+        <v>-0.5533757491308974</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.46153719840567</v>
+        <v>2.414537719355877</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.907304701966225</v>
+        <v>-5.036715587616958</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6216405837348316</v>
+        <v>0.5698762294745383</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4936141685750834</v>
+        <v>-0.5719466336580712</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.288750387690019</v>
+        <v>2.241750908640226</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.748110429909648</v>
+        <v>-4.877521315560381</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.805467953276668</v>
+        <v>0.7537035990163745</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4936141685750834</v>
+        <v>-0.5719466336580712</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.408900048409225</v>
+        <v>2.361900569359432</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.834709012890751</v>
+        <v>-4.964119898541484</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7853415461865496</v>
+        <v>0.7335771919262564</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4936141685750834</v>
+        <v>-0.5719466336580712</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.423413074511548</v>
+        <v>2.376413595461755</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.7963253503326</v>
+        <v>-4.925736235983333</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7981144525521788</v>
+        <v>0.7463500982918856</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4552305060169322</v>
+        <v>-0.53356297109992</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.443862713388807</v>
+        <v>2.396863234339014</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.619209020297434</v>
+        <v>-4.748619905948167</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8656900134115473</v>
+        <v>0.8139256591512538</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4552305060169322</v>
+        <v>-0.53356297109992</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.440591742234109</v>
+        <v>2.393592263184316</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.58950689632114</v>
+        <v>-4.718917781971873</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8782542547639778</v>
+        <v>0.8264899005036845</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4597006312322456</v>
+        <v>-0.5380330963152333</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.438593058866834</v>
+        <v>2.391593579817041</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.410131475082372</v>
+        <v>-4.539542360733106</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9437913985658992</v>
+        <v>0.892027044305606</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3029238730615269</v>
+        <v>-0.3812563381445147</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.52644608907568</v>
+        <v>2.479446610025887</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452236</v>
+        <v>3.716988143452234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.455145688602979</v>
+        <v>-4.584556574253712</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9065931684892463</v>
+        <v>0.8548288142289531</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3332727683761315</v>
+        <v>-0.4116052334591193</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.489044207218507</v>
+        <v>2.442044728168714</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.841500630401089</v>
+        <v>3.49115757166606</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.826111852614932</v>
+        <v>2.559127524302734</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.455145688602979</v>
+        <v>-4.584556574253712</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9065931684892463</v>
+        <v>0.8548288142289531</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3332727683761315</v>
+        <v>-0.4116052334591193</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.8191756496013</v>
+        <v>2.552191321289102</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240509.xlsx
+++ b/tame_output/ON/bt/strategyON_20240509.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-42.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.5%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>134.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-55.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.9%</t>
+          <t>444.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.0%</t>
+          <t>-615.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.7%</t>
+          <t>-288.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.2%</t>
+          <t>-272.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-190.8%</t>
+          <t>-205.7%</t>
         </is>
       </c>
     </row>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.238494834475917</v>
+        <v>-8.92611890494824</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5826185078159245</v>
+        <v>-0.4576681360048536</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.621496223218548</v>
+        <v>-9.309120293690871</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7359211646345609</v>
+        <v>-0.61097079282349</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.778895103431669</v>
+        <v>-9.466519173903992</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7963092007483792</v>
+        <v>-0.6713588289373082</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13842542593567</v>
+        <v>-9.826049496407993</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9347710264519291</v>
+        <v>-0.8098206546408586</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46482545460068</v>
+        <v>-10.15244952507301</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.057415017960758</v>
+        <v>-0.9324646461496866</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68397442267488</v>
+        <v>-10.3715984931472</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.142032854568667</v>
+        <v>-1.017082482757596</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.68028349771847</v>
+        <v>-10.36790756819079</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.140556484586103</v>
+        <v>-1.015606112775032</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88454167304833</v>
+        <v>-10.57216574352066</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.216746557599406</v>
+        <v>-1.091796185788335</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10257944467951</v>
+        <v>-10.79020351515183</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.299479111767441</v>
+        <v>-1.17452873995637</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02910961301206</v>
+        <v>-10.71673368348439</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254719477607041</v>
+        <v>-1.12976910579597</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20423403039861</v>
+        <v>-10.89185810087093</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.310214023814141</v>
+        <v>-1.18526365200307</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4386861244131</v>
+        <v>-11.12631019488542</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.411214026321533</v>
+        <v>-1.286263654510462</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72648996895033</v>
+        <v>-11.41411403942266</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.533007754910404</v>
+        <v>-1.408057383099333</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95631441611416</v>
+        <v>-11.64393848658648</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623821743937378</v>
+        <v>-1.498871372126307</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18834333585042</v>
+        <v>-11.87596740632274</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713939583202768</v>
+        <v>-1.588989211391697</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13632782188161</v>
+        <v>-11.82395189235393</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.689143041928842</v>
+        <v>-1.564192670117771</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27799966360573</v>
+        <v>-11.96562373407805</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.747287005517232</v>
+        <v>-1.622336633706161</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.22840881918089</v>
+        <v>-11.91603288965322</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.712397257582426</v>
+        <v>-1.587446885771355</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.02925671194379</v>
+        <v>-11.71688078241612</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645787548334269</v>
+        <v>-1.520837176523198</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80341155922438</v>
+        <v>-11.49103562969671</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.545870414210296</v>
+        <v>-1.420920042399226</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.67883290288679</v>
+        <v>-11.36645697335912</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494899807119201</v>
+        <v>-1.36994943530813</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73172819093108</v>
+        <v>-11.4193522614034</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.513424148174807</v>
+        <v>-1.388473776363737</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44781946000233</v>
+        <v>-11.13544353047465</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.394126951564671</v>
+        <v>-1.269176579753601</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37645306739268</v>
+        <v>-11.06407713786501</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.375317656914677</v>
+        <v>-1.250367285103607</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11261620018861</v>
+        <v>-10.80024027066094</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279666391345957</v>
+        <v>-1.154716019534887</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84537439932021</v>
+        <v>-10.53299846979254</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174604231497972</v>
+        <v>-1.049653859686902</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74746736064372</v>
+        <v>-10.43509143111605</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.135741731000837</v>
+        <v>-1.010791359189766</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.72351381966777</v>
+        <v>-10.41113789014009</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.12549180846496</v>
+        <v>-1.00054143665389</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.45945388134497</v>
+        <v>-10.14707795181729</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.033128149297593</v>
+        <v>-0.9081777774865225</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.740267896856324</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.752374257840131</v>
+        <v>-9.439998328312456</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.753083333555959</v>
+        <v>-0.6281329617448885</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.712189959473941</v>
+        <v>-9.399814029946265</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7366659903216415</v>
+        <v>-0.611715618510571</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.632120163936136</v>
+        <v>-9.319744234408461</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7052712508857626</v>
+        <v>-0.5803208790746925</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.398638941706537</v>
+        <v>-9.086263012178861</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6039543331560706</v>
+        <v>-0.4790039613450001</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.218930411562663</v>
+        <v>-8.906554482034988</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5349631314114802</v>
+        <v>-0.4100127596004102</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.086654937931776</v>
+        <v>-8.7742790084041</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4866854552120983</v>
+        <v>-0.3617350834010282</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.896055263258623</v>
+        <v>-8.583679333730947</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4076305246552003</v>
+        <v>-0.2826801528441298</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.647055464575041</v>
+        <v>-8.334679535047366</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2951242639581091</v>
+        <v>-0.1701738921470386</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.752645454348146</v>
+        <v>-8.44026952482047</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4653361894665693</v>
+        <v>-0.3403858176554992</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.771380356466743</v>
+        <v>-8.459004426939067</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4242858084369221</v>
+        <v>-0.2993354366258516</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.623440315059144</v>
+        <v>-8.311064385531468</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4849887145620499</v>
+        <v>-0.3600383427509795</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.599211678670171</v>
+        <v>-8.286835749142496</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4840112462599389</v>
+        <v>-0.3590608744488688</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.55566327189948</v>
+        <v>-8.243287342371804</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4735524956467554</v>
+        <v>-0.3486021238356853</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.313514878445622</v>
+        <v>-8.001138948917946</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.362230783884069</v>
+        <v>-0.237280412072999</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.250285506677274</v>
+        <v>-7.937909577149598</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.342406914717535</v>
+        <v>-0.2174565429064645</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.126994371860144</v>
+        <v>-7.814618442332467</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2955923667801064</v>
+        <v>-0.1706419949690354</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.105845172956702</v>
+        <v>-7.793469243429024</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.279431708981404</v>
+        <v>-0.1544813371703331</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.862079730973258</v>
+        <v>-7.549703801445579</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.186144823840976</v>
+        <v>-0.06119445202990459</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.598051663779998</v>
+        <v>-7.285675734252319</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.0784092830436558</v>
+        <v>0.04654108876741558</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.348201269830923</v>
+        <v>-7.035825340303244</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01427294951967584</v>
+        <v>0.1392233213307477</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.172309177363491</v>
+        <v>-6.859933247835812</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08822891002729749</v>
+        <v>0.2131792818383693</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.000862714341028</v>
+        <v>-6.688486784813349</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1701350012908365</v>
+        <v>0.2950853731019083</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.775829714672205</v>
+        <v>-6.463453785144526</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.259168678774663</v>
+        <v>0.3841190505857344</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.561195337035798</v>
+        <v>-6.248819407508119</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.349717230883543</v>
+        <v>0.4746676026946144</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.4681952958299</v>
+        <v>-6.155819366302221</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3681115061496976</v>
+        <v>0.4930618779607694</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.22776479902504</v>
+        <v>-5.91538886949736</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4660267814965193</v>
+        <v>0.5909771533075912</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.155522230853845</v>
+        <v>-5.843146301326166</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.4988531225998174</v>
+        <v>0.6238034944108892</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.03958238122866</v>
+        <v>-5.72720645170098</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5459076463672314</v>
+        <v>0.6708580181783033</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7928545650463659</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.884926612365134</v>
+        <v>-5.572550682837455</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6047680251326355</v>
+        <v>0.7297183969437069</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7928545650463659</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.664905814328123</v>
+        <v>-5.352529884800444</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.6943553813580539</v>
+        <v>0.8193057531691252</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6516347199783856</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.465657184423314</v>
+        <v>-5.153281254895635</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.7899490161218008</v>
+        <v>0.9148993879328722</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6516347199783856</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.306142080903944</v>
+        <v>-4.993766151376265</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8549009019698506</v>
+        <v>0.979851273780922</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4921196164590157</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.161469935804207</v>
+        <v>-4.849094006276528</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9228578625711852</v>
+        <v>1.047808234382257</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3474474713592783</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.221344763161899</v>
+        <v>-4.90896883363422</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8849454230295342</v>
+        <v>1.009895794840606</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4073222987169704</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.13454526538289</v>
+        <v>-4.822169335855211</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9420657154637038</v>
+        <v>1.067016087274776</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4073222987169704</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.137014971844696</v>
+        <v>-4.824639042317017</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9411502342523939</v>
+        <v>1.066100606063465</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4097920051787766</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.205385158168706</v>
+        <v>-4.893009228641027</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9248090821974917</v>
+        <v>1.049759454008563</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4005163061425616</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.08396872854223</v>
+        <v>-4.771592799014551</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9638123626799735</v>
+        <v>1.088762734491045</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4005163061425616</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.114961887870935</v>
+        <v>-4.802585958343256</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7761246639888784</v>
+        <v>0.9010750357999497</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4005163061425616</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.939487628078465</v>
+        <v>-4.627111698550786</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8508815998976538</v>
+        <v>0.9758319717087254</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.050423880719714</v>
+        <v>-4.738047951192035</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7822491276023613</v>
+        <v>0.9071994994134329</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.253450458262948</v>
+        <v>-4.941074528735268</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7041698818049738</v>
+        <v>0.8291202536160451</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.095524859327655</v>
+        <v>-4.783148929799975</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7775125078112231</v>
+        <v>0.9024628796222949</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.243846113138783</v>
+        <v>-4.931470183611104</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7131302768606318</v>
+        <v>0.8380806486717036</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.245029197789844</v>
+        <v>-4.932653268262165</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7044328184447335</v>
+        <v>0.8293831902558049</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.121901490795761</v>
+        <v>-4.809525561268082</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7542357742754682</v>
+        <v>0.8791861460865398</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.029091009344901</v>
+        <v>-4.716715079817222</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7206326587471774</v>
+        <v>0.8455830305582492</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.980527957123871</v>
+        <v>-4.668152027596192</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7419313555601903</v>
+        <v>0.8668817273712621</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.867856738887621</v>
+        <v>-4.555480809359942</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7820755513664135</v>
+        <v>0.9070259231774851</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.755479737704948</v>
+        <v>-4.443103808177269</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8325176476701499</v>
+        <v>0.9574680194812215</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.953714306591679</v>
+        <v>-4.641338377064</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7647210218839966</v>
+        <v>0.8896713936950682</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.036715587616958</v>
+        <v>-4.724339658089279</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5698762294745383</v>
+        <v>0.6948266012856099</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.877521315560381</v>
+        <v>-4.565145386032702</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7537035990163745</v>
+        <v>0.8786539708274463</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.964119898541484</v>
+        <v>-4.651743969013805</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7335771919262564</v>
+        <v>0.858527563737328</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.925736235983333</v>
+        <v>-4.613360306455654</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7463500982918856</v>
+        <v>0.8713004701029572</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.748619905948167</v>
+        <v>-4.436243976420488</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8139256591512538</v>
+        <v>0.9388760309623256</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.718917781971873</v>
+        <v>-4.406541852444194</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8264899005036845</v>
+        <v>0.9514402723147561</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.539542360733106</v>
+        <v>-4.227166431205426</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.892027044305606</v>
+        <v>1.016977416116678</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3812563381445147</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.584556574253712</v>
+        <v>-4.272180644726033</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8548288142289531</v>
+        <v>0.9797791860400247</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.4116052334591193</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.49115757166606</v>
+        <v>3.885561952960604</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.559127524302734</v>
+        <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.584556574253712</v>
+        <v>-4.543485655065435</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8548288142289531</v>
+        <v>0.8769487442432096</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4116052334591193</v>
+        <v>-0.4858412117892659</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.552191321289102</v>
+        <v>2.403194703509572</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240509.xlsx
+++ b/tame_output/ON/bt/strategyON_20240509.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.1%</t>
+          <t>444.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.9%</t>
+          <t>-607.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-288.5%</t>
+          <t>-285.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-154.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-272.6%</t>
+          <t>-284.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-205.7%</t>
+          <t>-213.0%</t>
         </is>
       </c>
     </row>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.92611890494824</v>
+        <v>-8.928390115581111</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4576681360048536</v>
+        <v>-0.4585766202580022</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.309120293690871</v>
+        <v>-9.311391504323742</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.61097079282349</v>
+        <v>-0.6118792770766386</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.466519173903992</v>
+        <v>-9.468790384536863</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6713588289373082</v>
+        <v>-0.6722673131904568</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.826049496407993</v>
+        <v>-9.828320707040865</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8098206546408586</v>
+        <v>-0.8107291388940072</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.15244952507301</v>
+        <v>-10.15472073570588</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9324646461496866</v>
+        <v>-0.9333731304028352</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.3715984931472</v>
+        <v>-10.37386970378008</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.017082482757596</v>
+        <v>-1.017990967010745</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.36790756819079</v>
+        <v>-10.37017877882366</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.015606112775032</v>
+        <v>-1.016514597028181</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.57216574352066</v>
+        <v>-10.57443695415353</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.091796185788335</v>
+        <v>-1.092704670041484</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.79020351515183</v>
+        <v>-10.79247472578471</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.17452873995637</v>
+        <v>-1.175437224209519</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.71673368348439</v>
+        <v>-10.71900489411726</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.12976910579597</v>
+        <v>-1.130677590049118</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.89185810087093</v>
+        <v>-10.8941293115038</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.18526365200307</v>
+        <v>-1.186172136256219</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.12631019488542</v>
+        <v>-11.12858140551829</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.286263654510462</v>
+        <v>-1.287172138763611</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.41411403942266</v>
+        <v>-11.41638525005553</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.408057383099333</v>
+        <v>-1.408965867352482</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.64393848658648</v>
+        <v>-11.64620969721935</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.498871372126307</v>
+        <v>-1.499779856379456</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.87596740632274</v>
+        <v>-11.87823861695562</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.588989211391697</v>
+        <v>-1.589897695644846</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.82395189235393</v>
+        <v>-11.8262231029868</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.564192670117771</v>
+        <v>-1.56510115437092</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.96562373407805</v>
+        <v>-11.96789494471092</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.622336633706161</v>
+        <v>-1.62324511795931</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.91603288965322</v>
+        <v>-11.91830410028609</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.587446885771355</v>
+        <v>-1.588355370024504</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.71688078241612</v>
+        <v>-11.71915199304899</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.520837176523198</v>
+        <v>-1.521745660776347</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.49103562969671</v>
+        <v>-11.49330684032958</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.420920042399226</v>
+        <v>-1.421828526652373</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.36645697335912</v>
+        <v>-11.36872818399199</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.36994943530813</v>
+        <v>-1.370857919561278</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.4193522614034</v>
+        <v>-11.42162347203627</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.388473776363737</v>
+        <v>-1.389382260616885</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.13544353047465</v>
+        <v>-11.13771474110752</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.269176579753601</v>
+        <v>-1.270085064006749</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.06407713786501</v>
+        <v>-11.06634834849788</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.250367285103607</v>
+        <v>-1.251275769356755</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.80024027066094</v>
+        <v>-10.80251148129381</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.154716019534887</v>
+        <v>-1.155624503788034</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.53299846979254</v>
+        <v>-10.53526968042541</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.049653859686902</v>
+        <v>-1.05056234394005</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.43509143111605</v>
+        <v>-10.43736264174892</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.010791359189766</v>
+        <v>-1.011699843442914</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.41113789014009</v>
+        <v>-10.41340910077296</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.00054143665389</v>
+        <v>-1.001449920907037</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.14707795181729</v>
+        <v>-10.14934916245016</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9081777774865225</v>
+        <v>-0.9090862617396702</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.740267896856324</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.439998328312456</v>
+        <v>-9.442269538945325</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6281329617448885</v>
+        <v>-0.6290414459980367</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.399814029946265</v>
+        <v>-9.402085240579135</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.611715618510571</v>
+        <v>-0.6126241027637191</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.319744234408461</v>
+        <v>-9.32201544504133</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5803208790746925</v>
+        <v>-0.5812293633278403</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.086263012178861</v>
+        <v>-9.088534222811731</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4790039613450001</v>
+        <v>-0.4799124455981483</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.906554482034988</v>
+        <v>-8.908825692667858</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4100127596004102</v>
+        <v>-0.4109212438535579</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.7742790084041</v>
+        <v>-8.77655021903697</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3617350834010282</v>
+        <v>-0.3626435676541759</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.583679333730947</v>
+        <v>-8.585950544363817</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2826801528441298</v>
+        <v>-0.283588637097278</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.334679535047366</v>
+        <v>-8.336950745680236</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1701738921470386</v>
+        <v>-0.1710823764001868</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.44026952482047</v>
+        <v>-8.44254073545334</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3403858176554992</v>
+        <v>-0.341294301908647</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.459004426939067</v>
+        <v>-8.461275637571937</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2993354366258516</v>
+        <v>-0.3002439208789998</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.311064385531468</v>
+        <v>-8.313335596164338</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3600383427509795</v>
+        <v>-0.3609468270041276</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.286835749142496</v>
+        <v>-8.289106959775365</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3590608744488688</v>
+        <v>-0.3599693587020165</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.243287342371804</v>
+        <v>-8.245558553004674</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3486021238356853</v>
+        <v>-0.3495106080888331</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.001138948917946</v>
+        <v>-8.003410159550816</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.237280412072999</v>
+        <v>-0.2381888963261467</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.937909577149598</v>
+        <v>-7.940180787782467</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2174565429064645</v>
+        <v>-0.2183650271596127</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.814618442332467</v>
+        <v>-7.816889652965337</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1706419949690354</v>
+        <v>-0.1715504792221831</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.793469243429024</v>
+        <v>-7.795740454061893</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1544813371703331</v>
+        <v>-0.1553898214234808</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.549703801445579</v>
+        <v>-7.551975012078449</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.06119445202990459</v>
+        <v>-0.0621029362830523</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.285675734252319</v>
+        <v>-7.287946944885189</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04654108876741558</v>
+        <v>0.04563260451426787</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.035825340303244</v>
+        <v>-7.038096550936114</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1392233213307477</v>
+        <v>0.1383148370776</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.859933247835812</v>
+        <v>-6.862204458468682</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2131792818383693</v>
+        <v>0.2122707975852212</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.688486784813349</v>
+        <v>-6.690757995446218</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2950853731019083</v>
+        <v>0.2941768888487606</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.463453785144526</v>
+        <v>-6.465724995777395</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3841190505857344</v>
+        <v>0.3832105663325867</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.248819407508119</v>
+        <v>-6.251090618140989</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4746676026946144</v>
+        <v>0.4737591184414667</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.155819366302221</v>
+        <v>-6.15809057693509</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4930618779607694</v>
+        <v>0.4921533937076217</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.91538886949736</v>
+        <v>-5.91766008013023</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5909771533075912</v>
+        <v>0.590068669054443</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.843146301326166</v>
+        <v>-5.845417511959035</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6238034944108892</v>
+        <v>0.6228950101577411</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.72720645170098</v>
+        <v>-5.72947766233385</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6708580181783033</v>
+        <v>0.6699495339251551</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7928545650463659</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.572550682837455</v>
+        <v>-5.486822073910687</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7297183969437069</v>
+        <v>0.7640098405144138</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7928545650463659</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.352529884800444</v>
+        <v>-5.266801275873677</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8193057531691252</v>
+        <v>0.8535971967398321</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6516347199783856</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.153281254895635</v>
+        <v>-5.067552645968868</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9148993879328722</v>
+        <v>0.9491908315035791</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6516347199783856</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.993766151376265</v>
+        <v>-4.908037542449498</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.979851273780922</v>
+        <v>1.014142717351629</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4921196164590157</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.849094006276528</v>
+        <v>-4.76336539734976</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.047808234382257</v>
+        <v>1.082099677952964</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3474474713592783</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.90896883363422</v>
+        <v>-4.823240224707453</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.009895794840606</v>
+        <v>1.044187238411313</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4073222987169704</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.822169335855211</v>
+        <v>-4.736440726928445</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.067016087274776</v>
+        <v>1.101307530845482</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4073222987169704</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.824639042317017</v>
+        <v>-4.738910433390251</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.066100606063465</v>
+        <v>1.100392049634172</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4097920051787766</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.893009228641027</v>
+        <v>-4.807280619714261</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.049759454008563</v>
+        <v>1.08405089757927</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4005163061425616</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.771592799014551</v>
+        <v>-4.685864190087784</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.088762734491045</v>
+        <v>1.123054178061752</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4005163061425616</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.802585958343256</v>
+        <v>-4.71685734941649</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9010750357999497</v>
+        <v>0.9353664793706564</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4005163061425616</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.627111698550786</v>
+        <v>-4.54138308962402</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9758319717087254</v>
+        <v>1.010123415279432</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.738047951192035</v>
+        <v>-4.652319342265269</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9071994994134329</v>
+        <v>0.9414909429841396</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.941074528735268</v>
+        <v>-4.855345919808502</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8291202536160451</v>
+        <v>0.8634116971867518</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.783148929799975</v>
+        <v>-4.697420320873209</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9024628796222949</v>
+        <v>0.9367543231930013</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.931470183611104</v>
+        <v>-4.845741574684338</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8380806486717036</v>
+        <v>0.8723720922424101</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.932653268262165</v>
+        <v>-4.846924659335398</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8293831902558049</v>
+        <v>0.8636746338265116</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.809525561268082</v>
+        <v>-4.723796952341315</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8791861460865398</v>
+        <v>0.9134775896572462</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.716715079817222</v>
+        <v>-4.630986470890456</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8455830305582492</v>
+        <v>0.8798744741289557</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.668152027596192</v>
+        <v>-4.582423418669426</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8668817273712621</v>
+        <v>0.9011731709419686</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.555480809359942</v>
+        <v>-4.469752200433176</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9070259231774851</v>
+        <v>0.9413173667481916</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.443103808177269</v>
+        <v>-4.357375199250503</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9574680194812215</v>
+        <v>0.991759463051928</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.641338377064</v>
+        <v>-4.555609768137233</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8896713936950682</v>
+        <v>0.9239628372657749</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.724339658089279</v>
+        <v>-4.638611049162512</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6948266012856099</v>
+        <v>0.7291180448563166</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.565145386032702</v>
+        <v>-4.479416777105936</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8786539708274463</v>
+        <v>0.9129454143981528</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.651743969013805</v>
+        <v>-4.566015360087039</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.858527563737328</v>
+        <v>0.8928190073080347</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.613360306455654</v>
+        <v>-4.527631697528887</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8713004701029572</v>
+        <v>0.9055919136736637</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.436243976420488</v>
+        <v>-4.350515367493721</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9388760309623256</v>
+        <v>0.9731674745330321</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.406541852444194</v>
+        <v>-4.320813243517428</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9514402723147561</v>
+        <v>0.9857317158854626</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.227166431205426</v>
+        <v>-4.14143782227866</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.016977416116678</v>
+        <v>1.051268859687384</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3812563381445147</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452234</v>
+        <v>3.716988143452235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.272180644726033</v>
+        <v>-4.186452035799267</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9797791860400247</v>
+        <v>1.014070629610731</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.4116052334591193</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.885561952960604</v>
+        <v>3.885561952960605</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.543485655065435</v>
+        <v>-4.455955471958307</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8769487442432096</v>
+        <v>0.9119608174860609</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4858412117892659</v>
+        <v>-0.607250983482587</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.403194703509572</v>
+        <v>2.330348840493579</v>
       </c>
     </row>
   </sheetData>
